--- a/healthcare_assessment_forms/016_vestibular_and_postural_assessment_quiz--healthcare_assessment_forms.xlsx
+++ b/healthcare_assessment_forms/016_vestibular_and_postural_assessment_quiz--healthcare_assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C111"/>
+  <dimension ref="A1:C110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>symptoms</t>
+          <t>nausea</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Symptoms</t>
+          <t>Nausea</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nausea</t>
+          <t>vomiting</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Nausea</t>
+          <t>Vomiting</t>
         </is>
       </c>
     </row>
@@ -1437,29 +1437,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>vomiting</t>
+          <t>diarrhea</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Vomiting</t>
+          <t>Diarrhea</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>postural_symptoms_choices</t>
+          <t>balance_activities_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>diarrhea</t>
+          <t>balance</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Diarrhea</t>
+          <t>Balance</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>balance</t>
+          <t>activity</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Balance</t>
+          <t>Activity</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>activity</t>
+          <t>postural</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Postural</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>postural</t>
+          <t>exercises</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Postural</t>
+          <t>Exercises</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>exercises</t>
+          <t>physical</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Exercises</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
@@ -1539,29 +1539,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>physical</t>
+          <t>activities</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Activities</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>balance_activities_choices</t>
+          <t>postural_positions_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>activities</t>
+          <t>postural</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Activities</t>
+          <t>Postural</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>postural</t>
+          <t>positions</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Postural</t>
+          <t>Positions</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>positions</t>
+          <t>standing</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Positions</t>
+          <t>Standing</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>standing</t>
+          <t>sitting</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Standing</t>
+          <t>Sitting</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>sitting</t>
+          <t>lying</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sitting</t>
+          <t>Lying</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>lying</t>
+          <t>kneeling</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lying</t>
+          <t>Kneeling</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>kneeling</t>
+          <t>supine</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kneeling</t>
+          <t>Supine</t>
         </is>
       </c>
     </row>
@@ -1675,29 +1675,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>supine</t>
+          <t>prone</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Supine</t>
+          <t>Prone</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>postural_positions_choices</t>
+          <t>postural_symptom_frequency_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>prone</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Prone</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1777,29 +1777,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>postural_symptom_frequency_choices</t>
+          <t>postural_symptom_severity_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1879,29 +1879,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>postural_symptom_severity_choices</t>
+          <t>vestibular_symptoms_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>vestibular</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Vestibular</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>vestibular</t>
+          <t>symptoms</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Vestibular</t>
+          <t>Symptoms</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>symptoms</t>
+          <t>tinnitus</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Symptoms</t>
+          <t>Tinnitus</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>tinnitus</t>
+          <t>dizziness</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tinnitus</t>
+          <t>Dizziness</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>dizziness</t>
+          <t>hearing</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dizziness</t>
+          <t>Hearing</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>hearing</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Hearing</t>
+          <t>Loss</t>
         </is>
       </c>
     </row>
@@ -1998,12 +1998,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>loss</t>
+          <t>balance</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Loss</t>
+          <t>Balance</t>
         </is>
       </c>
     </row>
@@ -2015,29 +2015,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>balance</t>
+          <t>problems</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Balance</t>
+          <t>Problems</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>vestibular_symptoms_choices</t>
+          <t>postural_symptoms_location_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>problems</t>
+          <t>right</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Problems</t>
+          <t>Right</t>
         </is>
       </c>
     </row>
@@ -2049,12 +2049,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Right</t>
+          <t>Left</t>
         </is>
       </c>
     </row>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Left</t>
+          <t>Center</t>
         </is>
       </c>
     </row>
@@ -2083,12 +2083,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>front</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Front</t>
         </is>
       </c>
     </row>
@@ -2100,29 +2100,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>front</t>
+          <t>back</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Front</t>
+          <t>Back</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>postural_symptoms_location_choices</t>
+          <t>head_position_choices</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>back</t>
+          <t>head</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Back</t>
+          <t>Head</t>
         </is>
       </c>
     </row>
@@ -2134,12 +2134,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>right</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Head</t>
+          <t>Right</t>
         </is>
       </c>
     </row>
@@ -2151,12 +2151,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Right</t>
+          <t>Left</t>
         </is>
       </c>
     </row>
@@ -2168,12 +2168,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Left</t>
+          <t>Center</t>
         </is>
       </c>
     </row>
@@ -2185,12 +2185,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>front</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Front</t>
         </is>
       </c>
     </row>
@@ -2202,29 +2202,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>front</t>
+          <t>back</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Front</t>
+          <t>Back</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>head_position_choices</t>
+          <t>postural_symptoms_frequency_1_choices</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>back</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Back</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2236,12 +2236,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2253,12 +2253,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -2270,12 +2270,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2287,29 +2287,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>postural_symptoms_frequency_1_choices</t>
+          <t>postural_symptoms_frequency_2_choices</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2338,12 +2338,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -2355,12 +2355,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2372,29 +2372,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>postural_symptoms_frequency_2_choices</t>
+          <t>postural_symptoms_frequency_3_choices</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2406,12 +2406,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2423,12 +2423,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2457,29 +2457,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>postural_symptoms_frequency_3_choices</t>
+          <t>postural_symptoms_frequency_4_choices</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2491,12 +2491,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2508,12 +2508,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -2525,12 +2525,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2542,29 +2542,29 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>postural_symptoms_frequency_4_choices</t>
+          <t>postural_symptoms_frequency_5_choices</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2576,12 +2576,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2593,12 +2593,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -2610,12 +2610,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2627,29 +2627,29 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>postural_symptoms_frequency_5_choices</t>
+          <t>postural_symptoms_location_1_choices</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>right</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Right</t>
         </is>
       </c>
     </row>
@@ -2661,12 +2661,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Right</t>
+          <t>Left</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Left</t>
+          <t>Center</t>
         </is>
       </c>
     </row>
@@ -2695,12 +2695,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>front</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Front</t>
         </is>
       </c>
     </row>
@@ -2712,29 +2712,29 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>front</t>
+          <t>back</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Front</t>
+          <t>Back</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>postural_symptoms_location_1_choices</t>
+          <t>postural_symptoms_location_2_choices</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>back</t>
+          <t>right</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Back</t>
+          <t>Right</t>
         </is>
       </c>
     </row>
@@ -2746,12 +2746,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Right</t>
+          <t>Left</t>
         </is>
       </c>
     </row>
@@ -2763,12 +2763,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Left</t>
+          <t>Center</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>front</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Front</t>
         </is>
       </c>
     </row>
@@ -2797,29 +2797,29 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>front</t>
+          <t>back</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Front</t>
+          <t>Back</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>postural_symptoms_location_2_choices</t>
+          <t>postural_symptoms_location_3_choices</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>back</t>
+          <t>right</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Back</t>
+          <t>Right</t>
         </is>
       </c>
     </row>
@@ -2831,12 +2831,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Right</t>
+          <t>Left</t>
         </is>
       </c>
     </row>
@@ -2848,12 +2848,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Left</t>
+          <t>Center</t>
         </is>
       </c>
     </row>
@@ -2865,12 +2865,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>front</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Front</t>
         </is>
       </c>
     </row>
@@ -2882,29 +2882,29 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>front</t>
+          <t>back</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Front</t>
+          <t>Back</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>postural_symptoms_location_3_choices</t>
+          <t>postural_symptoms_location_4_choices</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>back</t>
+          <t>right</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Back</t>
+          <t>Right</t>
         </is>
       </c>
     </row>
@@ -2916,12 +2916,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Right</t>
+          <t>Left</t>
         </is>
       </c>
     </row>
@@ -2933,12 +2933,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Left</t>
+          <t>Center</t>
         </is>
       </c>
     </row>
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>front</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Front</t>
         </is>
       </c>
     </row>
@@ -2967,27 +2967,10 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>front</t>
+          <t>back</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
-        <is>
-          <t>Front</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>postural_symptoms_location_4_choices</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>back</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
         <is>
           <t>Back</t>
         </is>
